--- a/database/BOM.xlsx
+++ b/database/BOM.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WILLIAM\Documents\liquidly-project\database\"/>
@@ -680,6 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/database/BOM.xlsx
+++ b/database/BOM.xlsx
@@ -23,287 +23,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="91">
   <si>
     <t>PC</t>
   </si>
   <si>
-    <t>AA00002273914</t>
-  </si>
-  <si>
-    <t>MODULO CEILLING EQUIPADO 4</t>
-  </si>
-  <si>
-    <t>AA00002281867</t>
-  </si>
-  <si>
-    <t>SM PAINEL MOD-1B</t>
-  </si>
-  <si>
-    <t>AA00002281897</t>
-  </si>
-  <si>
-    <t>AA00002281893</t>
-  </si>
-  <si>
-    <t>MOD-1B</t>
-  </si>
-  <si>
-    <t>AA00002274288</t>
-  </si>
-  <si>
-    <t>FOLHA DE ALUMINIO MOD-1B</t>
-  </si>
-  <si>
-    <t>AA00002274285</t>
-  </si>
-  <si>
-    <t>PERFIL CEILING 1596,5MM</t>
-  </si>
-  <si>
-    <t>AA00002253562</t>
-  </si>
-  <si>
-    <t>SUPORTE PIRALU</t>
-  </si>
-  <si>
-    <t>AA00002284877</t>
-  </si>
-  <si>
-    <t>SM SUPORTE CAMERA</t>
-  </si>
-  <si>
-    <t>AA00002280721</t>
-  </si>
-  <si>
     <t>SUPORTE CAMERA</t>
   </si>
   <si>
-    <t>DTR0000471764</t>
-  </si>
-  <si>
-    <t>REBITE ROSCADO FHO M5 0.5-3</t>
-  </si>
-  <si>
-    <t>LM00000277634</t>
-  </si>
-  <si>
-    <t>SIMSON ISR 70-08 AP</t>
-  </si>
-  <si>
-    <t>LM00000277629</t>
-  </si>
-  <si>
-    <t>SIMSON ISR 70-03 FR</t>
-  </si>
-  <si>
-    <t>LM00000276860</t>
-  </si>
-  <si>
-    <t>SIMSON ISR 7007</t>
-  </si>
-  <si>
-    <t>DTR0000257232</t>
-  </si>
-  <si>
-    <t>FITA ACRILICA ADES. ALU 72X0.18MM-20T79C</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
-    <t>AA00002274291</t>
-  </si>
-  <si>
-    <t>PAINEL CEILING PERFIL 1598,5MM</t>
-  </si>
-  <si>
-    <t>AA00002281866</t>
-  </si>
-  <si>
-    <t>ESPUMA DE CELOFANE 12 RFP700 AG</t>
-  </si>
-  <si>
-    <t>AA00002253582</t>
-  </si>
-  <si>
     <t>ANTIQUEDA</t>
   </si>
   <si>
-    <t>AA00002253588</t>
-  </si>
-  <si>
     <t>ETIQUETA CUIDADO</t>
   </si>
   <si>
-    <t>AA00002253586</t>
-  </si>
-  <si>
     <t>PRETECAO DE ARESTA</t>
   </si>
   <si>
-    <t>AA00002253583</t>
-  </si>
-  <si>
-    <t>AA00002310617</t>
-  </si>
-  <si>
-    <t>QTR TURN LOCK SOUTHCO E5-99-3070-10</t>
-  </si>
-  <si>
-    <t>NH00001787308</t>
-  </si>
-  <si>
-    <t>FITA ESPONJA EPDM FITA</t>
-  </si>
-  <si>
-    <t>CD00001864805</t>
-  </si>
-  <si>
-    <t>BORRACHA EPDM 3X2</t>
-  </si>
-  <si>
-    <t>DTR0009907822</t>
-  </si>
-  <si>
-    <t>PARAF HEX M4X12 ZN 0.15</t>
-  </si>
-  <si>
-    <t>DTR0009907737</t>
-  </si>
-  <si>
-    <t>PORCA HEX M4 ZN 0.15 8</t>
-  </si>
-  <si>
-    <t>DTR0009907273</t>
-  </si>
-  <si>
-    <t>ARRU. CS L M4 ZN 0.15</t>
-  </si>
-  <si>
-    <t>AA00002274236</t>
-  </si>
-  <si>
-    <t>PERFIL CEILING 3572MM</t>
-  </si>
-  <si>
-    <t>AA00002274213</t>
-  </si>
-  <si>
-    <t>PERFIL DIFUSOR DO CEILING 3200</t>
-  </si>
-  <si>
-    <t>AA00002274210</t>
-  </si>
-  <si>
-    <t>CEILING POLICARBONATO 3140MM</t>
-  </si>
-  <si>
-    <t>AA00002273915</t>
-  </si>
-  <si>
-    <t>ESTRUTURA DO CEILING MODULO 4</t>
-  </si>
-  <si>
-    <t>AA00002252534</t>
-  </si>
-  <si>
-    <t>SUPORTE Z</t>
-  </si>
-  <si>
-    <t>AA00002252478</t>
-  </si>
-  <si>
     <t>FECHAMENTO DE GAP</t>
   </si>
   <si>
-    <t>AA00002252479</t>
-  </si>
-  <si>
     <t>SUPORTE</t>
   </si>
   <si>
-    <t>DTR0000015396</t>
-  </si>
-  <si>
-    <t>VELCRO PRETO 25.4X2.9MM-29T93C</t>
-  </si>
-  <si>
-    <t>AA00002252468</t>
-  </si>
-  <si>
-    <t>AA00002252469</t>
-  </si>
-  <si>
-    <t>AA00002294765</t>
-  </si>
-  <si>
-    <t>SM SUPORTE TUBO LATERAL</t>
-  </si>
-  <si>
-    <t>AA00002294801</t>
-  </si>
-  <si>
-    <t>SUPORTE TUBO LATERAL 2</t>
-  </si>
-  <si>
-    <t>AA00002294675</t>
-  </si>
-  <si>
     <t>CHAPA PINTADA</t>
   </si>
   <si>
-    <t>DTR0000388840</t>
-  </si>
-  <si>
-    <t>REBITE ROSCADO FHO M6 1-3</t>
-  </si>
-  <si>
-    <t>AA00002290885</t>
-  </si>
-  <si>
-    <t>AA00002345920</t>
-  </si>
-  <si>
-    <t>SM SUPORTE TRANSVERSAL</t>
-  </si>
-  <si>
-    <t>AA00002345921</t>
-  </si>
-  <si>
-    <t>PERFIL CROSS BEAM DO CEILING 1440MM</t>
-  </si>
-  <si>
-    <t>DTR0009907851</t>
-  </si>
-  <si>
-    <t>PARAF HEX M8X20 FLZN 0.15</t>
-  </si>
-  <si>
-    <t>DTR0009907842</t>
-  </si>
-  <si>
-    <t>PARAFUSO H M6X25 ZN 0.15</t>
-  </si>
-  <si>
-    <t>DTR0009907841</t>
-  </si>
-  <si>
-    <t>PARAFUSO SEXTAVADO M6X20 ZN 0.15</t>
-  </si>
-  <si>
-    <t>DTR0009907741</t>
-  </si>
-  <si>
-    <t>PORCA HEX M10 FLZN 0.15 8</t>
-  </si>
-  <si>
-    <t>DTR0009907740</t>
-  </si>
-  <si>
-    <t>DTR0009907739</t>
-  </si>
-  <si>
     <t>project_id</t>
   </si>
   <si>
@@ -332,6 +80,222 @@
   </si>
   <si>
     <t>company_id</t>
+  </si>
+  <si>
+    <t>2273914</t>
+  </si>
+  <si>
+    <t>2281867</t>
+  </si>
+  <si>
+    <t>2281897</t>
+  </si>
+  <si>
+    <t>2281893</t>
+  </si>
+  <si>
+    <t>2274288</t>
+  </si>
+  <si>
+    <t>2274285</t>
+  </si>
+  <si>
+    <t>2253562</t>
+  </si>
+  <si>
+    <t>2284877</t>
+  </si>
+  <si>
+    <t>2280721</t>
+  </si>
+  <si>
+    <t>0471764</t>
+  </si>
+  <si>
+    <t>0277634</t>
+  </si>
+  <si>
+    <t>0277629</t>
+  </si>
+  <si>
+    <t>0276860</t>
+  </si>
+  <si>
+    <t>0257232</t>
+  </si>
+  <si>
+    <t>2274291</t>
+  </si>
+  <si>
+    <t>2281866</t>
+  </si>
+  <si>
+    <t>2253582</t>
+  </si>
+  <si>
+    <t>2253588</t>
+  </si>
+  <si>
+    <t>2253586</t>
+  </si>
+  <si>
+    <t>2253583</t>
+  </si>
+  <si>
+    <t>2310617</t>
+  </si>
+  <si>
+    <t>1787308</t>
+  </si>
+  <si>
+    <t>1864805</t>
+  </si>
+  <si>
+    <t>9907822</t>
+  </si>
+  <si>
+    <t>9907737</t>
+  </si>
+  <si>
+    <t>9907273</t>
+  </si>
+  <si>
+    <t>2274236</t>
+  </si>
+  <si>
+    <t>2274213</t>
+  </si>
+  <si>
+    <t>2274210</t>
+  </si>
+  <si>
+    <t>2273915</t>
+  </si>
+  <si>
+    <t>2252534</t>
+  </si>
+  <si>
+    <t>2252478</t>
+  </si>
+  <si>
+    <t>2252479</t>
+  </si>
+  <si>
+    <t>0015396</t>
+  </si>
+  <si>
+    <t>2252468</t>
+  </si>
+  <si>
+    <t>2252469</t>
+  </si>
+  <si>
+    <t>2294765</t>
+  </si>
+  <si>
+    <t>2294801</t>
+  </si>
+  <si>
+    <t>2294675</t>
+  </si>
+  <si>
+    <t>0388840</t>
+  </si>
+  <si>
+    <t>2290885</t>
+  </si>
+  <si>
+    <t>2345920</t>
+  </si>
+  <si>
+    <t>2345921</t>
+  </si>
+  <si>
+    <t>9907851</t>
+  </si>
+  <si>
+    <t>9907842</t>
+  </si>
+  <si>
+    <t>9907841</t>
+  </si>
+  <si>
+    <t>9907741</t>
+  </si>
+  <si>
+    <t>9907740</t>
+  </si>
+  <si>
+    <t>9907739</t>
+  </si>
+  <si>
+    <t>MODULO</t>
+  </si>
+  <si>
+    <t>PAINEL</t>
+  </si>
+  <si>
+    <t>PREGO</t>
+  </si>
+  <si>
+    <t>FOLHA DE ALUMINIO</t>
+  </si>
+  <si>
+    <t>SUPORTE 2</t>
+  </si>
+  <si>
+    <t>SUPORTE 3</t>
+  </si>
+  <si>
+    <t>REBITE</t>
+  </si>
+  <si>
+    <t>METAL</t>
+  </si>
+  <si>
+    <t>METAL2</t>
+  </si>
+  <si>
+    <t>METAL3</t>
+  </si>
+  <si>
+    <t>FITA</t>
+  </si>
+  <si>
+    <t>ESPUMA</t>
+  </si>
+  <si>
+    <t>TURN LOCK</t>
+  </si>
+  <si>
+    <t>FITA ESPONJA</t>
+  </si>
+  <si>
+    <t>BORRACHA</t>
+  </si>
+  <si>
+    <t>PARAFUSO</t>
+  </si>
+  <si>
+    <t>PORCA</t>
+  </si>
+  <si>
+    <t>PORCA 2</t>
+  </si>
+  <si>
+    <t>FITA ACRILICA</t>
+  </si>
+  <si>
+    <t>ESTRUTURA</t>
+  </si>
+  <si>
+    <t>VELCRO</t>
+  </si>
+  <si>
+    <t>PARAFUSO2</t>
+  </si>
+  <si>
+    <t>PARAFUSO3</t>
   </si>
 </sst>
 </file>
@@ -686,7 +650,7 @@
   <cols>
     <col min="1" max="1" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="1"/>
     <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -694,31 +658,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -726,10 +690,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -741,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H2">
         <f>D2</f>
@@ -756,10 +720,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -771,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H3">
         <f t="shared" ref="H3:H50" si="0">D3</f>
@@ -786,10 +750,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -801,7 +765,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
@@ -816,10 +780,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -831,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
@@ -846,10 +810,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -861,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
@@ -876,10 +840,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -891,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
@@ -906,10 +870,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -921,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
@@ -936,10 +900,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -951,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
@@ -966,10 +930,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -981,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H10">
         <f t="shared" si="0"/>
@@ -996,10 +960,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -1011,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H11">
         <f t="shared" si="0"/>
@@ -1026,10 +990,10 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1041,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H12">
         <f t="shared" si="0"/>
@@ -1056,10 +1020,10 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1071,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
@@ -1086,10 +1050,10 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" t="s">
-        <v>25</v>
+        <v>31</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -1101,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
@@ -1116,22 +1080,22 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="D15">
         <v>0.4</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F15" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H15">
         <f t="shared" si="0"/>
@@ -1146,10 +1110,10 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1161,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H16">
         <f t="shared" si="0"/>
@@ -1176,10 +1140,10 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1191,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H17">
         <f t="shared" si="0"/>
@@ -1206,10 +1170,10 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -1221,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H18">
         <f t="shared" si="0"/>
@@ -1236,10 +1200,10 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -1251,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H19">
         <f t="shared" si="0"/>
@@ -1269,7 +1233,7 @@
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1281,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H20">
         <f t="shared" si="0"/>
@@ -1296,10 +1260,10 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -1311,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H21">
         <f t="shared" si="0"/>
@@ -1326,10 +1290,10 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1341,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H22">
         <f t="shared" si="0"/>
@@ -1356,22 +1320,22 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F23" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H23">
         <f t="shared" si="0"/>
@@ -1386,10 +1350,10 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -1401,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H24">
         <f t="shared" si="0"/>
@@ -1416,10 +1380,10 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D25">
         <v>4</v>
@@ -1431,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H25">
         <f t="shared" si="0"/>
@@ -1446,10 +1410,10 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -1461,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H26">
         <f t="shared" si="0"/>
@@ -1476,10 +1440,10 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -1491,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H27">
         <f t="shared" si="0"/>
@@ -1506,22 +1470,22 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="D28">
         <v>9.4</v>
       </c>
       <c r="E28" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F28" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H28">
         <f t="shared" si="0"/>
@@ -1536,10 +1500,10 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" t="s">
-        <v>53</v>
+        <v>46</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1551,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H29">
         <f t="shared" si="0"/>
@@ -1566,10 +1530,10 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" t="s">
-        <v>55</v>
+        <v>47</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -1581,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H30">
         <f t="shared" si="0"/>
@@ -1596,10 +1560,10 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
+        <v>48</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -1611,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H31">
         <f t="shared" si="0"/>
@@ -1626,10 +1590,10 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1641,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H32">
         <f t="shared" si="0"/>
@@ -1656,10 +1620,10 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -1671,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H33">
         <f t="shared" si="0"/>
@@ -1686,10 +1650,10 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -1701,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H34">
         <f t="shared" si="0"/>
@@ -1716,10 +1680,10 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -1731,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H35">
         <f t="shared" si="0"/>
@@ -1746,22 +1710,22 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D36">
         <v>0.16</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F36" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H36">
         <f t="shared" si="0"/>
@@ -1776,10 +1740,10 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -1791,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H37">
         <f t="shared" si="0"/>
@@ -1806,10 +1770,10 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1821,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H38">
         <f t="shared" si="0"/>
@@ -1836,22 +1800,22 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" t="s">
-        <v>67</v>
+        <v>56</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="D39">
         <v>0.16</v>
       </c>
       <c r="E39" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F39" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H39">
         <f t="shared" si="0"/>
@@ -1866,10 +1830,10 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" t="s">
-        <v>71</v>
+        <v>57</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="D40">
         <v>8</v>
@@ -1881,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H40">
         <f t="shared" si="0"/>
@@ -1896,10 +1860,10 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" t="s">
-        <v>73</v>
+        <v>58</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -1911,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H41">
         <f t="shared" si="0"/>
@@ -1926,10 +1890,10 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -1941,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H42">
         <f t="shared" si="0"/>
@@ -1956,10 +1920,10 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D43">
         <v>8</v>
@@ -1971,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H43">
         <f t="shared" si="0"/>
@@ -1986,10 +1950,10 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="D44">
         <v>8</v>
@@ -2001,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H44">
         <f t="shared" si="0"/>
@@ -2016,10 +1980,10 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2031,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H45">
         <f t="shared" si="0"/>
@@ -2046,10 +2010,10 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -2061,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H46">
         <f t="shared" si="0"/>
@@ -2076,10 +2040,10 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D47">
         <v>40</v>
@@ -2091,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H47">
         <f t="shared" si="0"/>
@@ -2106,10 +2070,10 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" t="s">
         <v>89</v>
-      </c>
-      <c r="C48" t="s">
-        <v>86</v>
       </c>
       <c r="D48">
         <v>16</v>
@@ -2121,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H48">
         <f t="shared" si="0"/>
@@ -2136,10 +2100,10 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" t="s">
-        <v>88</v>
+        <v>66</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2151,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H49">
         <f t="shared" si="0"/>
@@ -2166,10 +2130,10 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D50">
         <v>10</v>
@@ -2181,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H50">
         <f t="shared" si="0"/>
